--- a/data/trans_bre/P6901-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 17,96</t>
+          <t>-16,24; 17,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 27,96</t>
+          <t>-3,45; 26,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 29,67</t>
+          <t>-5,29; 30,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 17,57</t>
+          <t>-11,22; 17,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 25,13</t>
+          <t>-19,09; 24,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 42,93</t>
+          <t>-3,97; 40,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 48,84</t>
+          <t>-5,58; 50,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 26,35</t>
+          <t>-13,23; 26,07</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 18,23</t>
+          <t>-8,85; 18,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 17,72</t>
+          <t>-11,32; 15,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 28,84</t>
+          <t>2,02; 27,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 19,58</t>
+          <t>-4,0; 18,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 27,68</t>
+          <t>-11,32; 28,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 24,75</t>
+          <t>-12,98; 22,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 43,34</t>
+          <t>2,92; 42,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 30,9</t>
+          <t>-5,12; 29,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 20,94</t>
+          <t>-5,25; 20,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 16,26</t>
+          <t>-16,32; 16,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 16,42</t>
+          <t>-5,96; 17,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 27,95</t>
+          <t>-9,42; 28,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 29,41</t>
+          <t>-6,05; 28,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 25,46</t>
+          <t>-20,2; 25,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 22,24</t>
+          <t>-6,69; 23,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 46,11</t>
+          <t>-12,03; 45,44</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 9,58</t>
+          <t>-13,18; 9,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 15,3</t>
+          <t>-16,17; 14,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 24,66</t>
+          <t>-3,62; 25,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 15,01</t>
+          <t>-14,08; 14,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 13,59</t>
+          <t>-16,56; 13,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 22,46</t>
+          <t>-20,04; 22,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 42,15</t>
+          <t>-4,45; 42,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 23,69</t>
+          <t>-17,93; 23,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,7</t>
+          <t>-3,94; 9,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 11,08</t>
+          <t>-3,46; 10,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 16,95</t>
+          <t>3,66; 17,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 13,76</t>
+          <t>-3,01; 13,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 13,49</t>
+          <t>-5,03; 13,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 15,56</t>
+          <t>-4,45; 15,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 24,51</t>
+          <t>4,84; 24,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 20,14</t>
+          <t>-3,74; 18,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6901-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 17,4</t>
+          <t>-14,48; 17,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 26,93</t>
+          <t>-3,68; 27,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 30,96</t>
+          <t>-7,44; 27,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 17,62</t>
+          <t>-9,69; 19,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 24,25</t>
+          <t>-18,0; 25,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 40,23</t>
+          <t>-4,64; 42,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 50,47</t>
+          <t>-9,04; 44,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 26,07</t>
+          <t>-11,49; 29,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,68</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 18,7</t>
+          <t>-7,71; 17,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 15,75</t>
+          <t>-11,57; 16,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 27,89</t>
+          <t>3,27; 27,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 18,89</t>
+          <t>-4,57; 15,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 28,4</t>
+          <t>-10,34; 25,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 22,66</t>
+          <t>-14,16; 23,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 42,74</t>
+          <t>4,21; 41,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 29,36</t>
+          <t>-5,78; 22,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>-5,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>-6,34%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 20,15</t>
+          <t>-5,78; 19,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 16,9</t>
+          <t>-16,2; 15,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 17,6</t>
+          <t>-7,5; 16,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 28,26</t>
+          <t>-19,76; 9,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 28,96</t>
+          <t>-7,15; 27,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 25,72</t>
+          <t>-20,75; 23,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 23,06</t>
+          <t>-8,82; 21,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 45,44</t>
+          <t>-23,28; 12,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 9,75</t>
+          <t>-14,62; 9,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 14,82</t>
+          <t>-14,8; 14,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 25,19</t>
+          <t>-2,93; 25,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 14,37</t>
+          <t>-6,47; 16,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 13,73</t>
+          <t>-17,99; 12,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 22,61</t>
+          <t>-18,82; 21,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 42,25</t>
+          <t>-4,17; 42,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 23,0</t>
+          <t>-8,32; 27,02</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,67</t>
+          <t>-3,69; 9,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,73</t>
+          <t>-4,49; 11,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 17,31</t>
+          <t>3,19; 17,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 13,01</t>
+          <t>-3,92; 8,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 13,3</t>
+          <t>-4,71; 13,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 15,32</t>
+          <t>-6,04; 16,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 24,41</t>
+          <t>3,99; 24,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 18,93</t>
+          <t>-5,08; 12,12</t>
         </is>
       </c>
     </row>
